--- a/education_forms/048_educational_leadership_think_tank_application_form--education_forms.xlsx
+++ b/education_forms/048_educational_leadership_think_tank_application_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -827,8 +827,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -856,12 +856,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'teacher',_'value':_'teacher'}</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Teacher', 'value': 'teacher'}</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'principal/dean',_'value':_'principal-dean'}</t>
+          <t>principal/dean</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Principal/Dean', 'value': 'principal-dean'}</t>
+          <t>Principal/Dean</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'superintendent/dean',_'value':_'superintendent-dean'}</t>
+          <t>superintendent/dean</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Superintendent/Dean', 'value': 'superintendent-dean'}</t>
+          <t>Superintendent/Dean</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'teacher',_'value':_'teacher'}</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Teacher', 'value': 'teacher'}</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
@@ -924,12 +924,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'principal/dean',_'value':_'principal-dean'}</t>
+          <t>principal/dean</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Principal/Dean', 'value': 'principal-dean'}</t>
+          <t>Principal/Dean</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'superintendent/dean',_'value':_'superintendent-dean'}</t>
+          <t>superintendent/dean</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Superintendent/Dean', 'value': 'superintendent-dean'}</t>
+          <t>Superintendent/Dean</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
